--- a/Braintree/task_list_braintree.xlsx
+++ b/Braintree/task_list_braintree.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\Braintree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8A2BAB-4241-401C-9FE8-DA4C37D2D63B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9601E2-14D5-4E8B-B277-A906E1E942F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" activeTab="1" xr2:uid="{0988228D-CB65-49FF-A818-8D2DE82566F6}"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" activeTab="3" xr2:uid="{0988228D-CB65-49FF-A818-8D2DE82566F6}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
-    <sheet name="총계정원장" sheetId="2" r:id="rId2"/>
+    <sheet name="host1_총계정원장" sheetId="2" r:id="rId2"/>
+    <sheet name="host1_상세검색_시나리오" sheetId="3" r:id="rId3"/>
+    <sheet name="host1_벤포드법칙분석" sheetId="5" r:id="rId4"/>
+    <sheet name="host2_분개장AI분석" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="51">
   <si>
     <t>항목</t>
   </si>
@@ -104,6 +107,129 @@
   </si>
   <si>
     <t>상품매출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>순번</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정과목</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>적요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수관계자거래</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>주식회사 원더플레이스</t>
+  </si>
+  <si>
+    <t>금액 유형</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대변만</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>유형자산취득거래</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비품</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차변만</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>시설장치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>표시방식</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세내역</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행조회서완전성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이자비용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>단기차입금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>월합계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차변+대변 모두</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래방향</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반사항분석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공휴일전표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상대계정분석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차변</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대변</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미지급금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>월별트렌드분석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>금액 기준열</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보통예금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분석할 계정과목</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -664,4 +790,370 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193611D9-2EAA-4DF6-9B16-C177A651CEFE}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="21.9140625" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="20.9140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.9140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CE977AC-918C-48AD-A858-7636F2EFDC97}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="14.9140625" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4E540D-2F54-444B-8CC0-15566B81F298}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="16.1640625" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Braintree/task_list_braintree.xlsx
+++ b/Braintree/task_list_braintree.xlsx
@@ -8,16 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\Braintree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9601E2-14D5-4E8B-B277-A906E1E942F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AABC61B-657B-49A8-9530-2803087AA308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" activeTab="3" xr2:uid="{0988228D-CB65-49FF-A818-8D2DE82566F6}"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" firstSheet="3" activeTab="4" xr2:uid="{0988228D-CB65-49FF-A818-8D2DE82566F6}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
     <sheet name="host1_총계정원장" sheetId="2" r:id="rId2"/>
     <sheet name="host1_상세검색_시나리오" sheetId="3" r:id="rId3"/>
     <sheet name="host1_벤포드법칙분석" sheetId="5" r:id="rId4"/>
-    <sheet name="host2_분개장AI분석" sheetId="4" r:id="rId5"/>
+    <sheet name="host1_전기 데이터 비교 분석" sheetId="8" r:id="rId5"/>
+    <sheet name="host1_이중거래처분석" sheetId="6" r:id="rId6"/>
+    <sheet name="host1_외상매출매입상계" sheetId="7" r:id="rId7"/>
+    <sheet name="host2_분개장AI분석" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="52">
   <si>
     <t>항목</t>
   </si>
@@ -230,6 +233,10 @@
   </si>
   <si>
     <t>분석할 계정과목</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지급수수료</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1024,6 +1031,65 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{265A6539-2564-46BF-942B-EEC385B53B6D}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04D14481-7FF3-4693-99E5-2CB88F450E06}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F26966BA-9AA6-46A4-A0FC-D608B070C3C3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4E540D-2F54-444B-8CC0-15566B81F298}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
